--- a/data_clean/Diseases/incidence_table.xlsx
+++ b/data_clean/Diseases/incidence_table.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -523,13 +523,13 @@
         </is>
       </c>
       <c r="F5">
-        <v>73268.5586248076</v>
+        <v>2099.061971132804</v>
       </c>
       <c r="G5">
-        <v>44734.8500422552</v>
+        <v>1665.46979262609</v>
       </c>
       <c r="H5">
-        <v>110025.7650575368</v>
+        <v>2615.436767631871</v>
       </c>
     </row>
     <row r="6">
@@ -650,7 +650,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="F9">
-        <v>136239.9257642573</v>
+        <v>2715.452220243504</v>
       </c>
       <c r="G9">
-        <v>111507.8160492127</v>
+        <v>2156</v>
       </c>
       <c r="H9">
-        <v>160055.4324442564</v>
+        <v>3403.211977724929</v>
       </c>
     </row>
     <row r="10">
@@ -676,30 +676,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C10">
-        <v>3908726</v>
+        <v>3829648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>620.535443392571</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>824.974710621776</v>
       </c>
     </row>
     <row r="11">
@@ -710,30 +710,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C11">
-        <v>3908726</v>
+        <v>3829648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F11">
-        <v>97.07328864355</v>
+        <v>55558.8375973942</v>
       </c>
       <c r="G11">
-        <v>75.0821071306456</v>
+        <v>40104.2959711759</v>
       </c>
       <c r="H11">
-        <v>125.789689851057</v>
+        <v>75407</v>
       </c>
     </row>
     <row r="12">
@@ -744,30 +744,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C12">
-        <v>3908726</v>
+        <v>3829648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F12">
-        <v>2181.530399019817</v>
+        <v>15315.62840885514</v>
       </c>
       <c r="G12">
-        <v>1607.842169785802</v>
+        <v>11293.14798314826</v>
       </c>
       <c r="H12">
-        <v>2997.30917827754</v>
+        <v>20064</v>
       </c>
     </row>
     <row r="13">
@@ -778,30 +778,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C13">
-        <v>3908726</v>
+        <v>3829648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F13">
-        <v>22343.9775533641</v>
+        <v>32662.2447832973</v>
       </c>
       <c r="G13">
-        <v>14476.33538237788</v>
+        <v>23964</v>
       </c>
       <c r="H13">
-        <v>32524.8425429897</v>
+        <v>42697</v>
       </c>
     </row>
     <row r="14">
@@ -812,30 +812,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C14">
-        <v>3908726</v>
+        <v>3829648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F14">
-        <v>6147.365530298801</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>3945.64374713516</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>8599.254275415431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -846,30 +846,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C15">
-        <v>3908726</v>
+        <v>3829648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>136239.9257642573</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>111507.8160492127</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>160055.4324442564</v>
       </c>
     </row>
     <row r="16">
@@ -888,7 +888,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="F16">
-        <v>125679.2680024553</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>103946.7445125612</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>155227.1313639628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -922,41 +922,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>prevalence</t>
+          <t>incidence</t>
         </is>
       </c>
       <c r="F17">
-        <v>79276.89547348869</v>
+        <v>97.07328864355</v>
       </c>
       <c r="G17">
-        <v>63568.3063734423</v>
+        <v>75.0821071306456</v>
       </c>
       <c r="H17">
-        <v>94372.30382186361</v>
+        <v>125.789689851057</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C18">
-        <v>4096230</v>
+        <v>3908726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -965,32 +965,32 @@
         </is>
       </c>
       <c r="F18">
-        <v>2780.422601653696</v>
+        <v>2181.530399019817</v>
       </c>
       <c r="G18">
-        <v>2330.600014968618</v>
+        <v>1607.842169785802</v>
       </c>
       <c r="H18">
-        <v>3260.06439065651</v>
+        <v>2997.30917827754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C19">
-        <v>4096230</v>
+        <v>3908726</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -999,32 +999,32 @@
         </is>
       </c>
       <c r="F19">
-        <v>340.745943565134</v>
+        <v>2784.15011902699</v>
       </c>
       <c r="G19">
-        <v>274.2673331741521</v>
+        <v>2784.15011902699</v>
       </c>
       <c r="H19">
-        <v>420.161694727751</v>
+        <v>3512.58495742775</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C20">
-        <v>4096230</v>
+        <v>3908726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1033,32 +1033,32 @@
         </is>
       </c>
       <c r="F20">
-        <v>2289.499528412314</v>
+        <v>6147.365530298801</v>
       </c>
       <c r="G20">
-        <v>1827.303241610942</v>
+        <v>3945.64374713516</v>
       </c>
       <c r="H20">
-        <v>2851.59340962557</v>
+        <v>8599.254275415431</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C21">
-        <v>4096230</v>
+        <v>3908726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1067,32 +1067,32 @@
         </is>
       </c>
       <c r="F21">
-        <v>122474.7416998053</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>77334.8469309217</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>182606.205147626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C22">
-        <v>4096230</v>
+        <v>3908726</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1101,37 +1101,37 @@
         </is>
       </c>
       <c r="F22">
-        <v>5843.84219410092</v>
+        <v>125679.2680024553</v>
       </c>
       <c r="G22">
-        <v>3783.80070456914</v>
+        <v>103946.7445125612</v>
       </c>
       <c r="H22">
-        <v>8315.68691031983</v>
+        <v>155227.1313639628</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C23">
-        <v>4096230</v>
+        <v>3908726</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F23">
@@ -1147,54 +1147,54 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C24">
-        <v>4096230</v>
+        <v>3908726</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F24">
-        <v>233272.265423371</v>
+        <v>746.6469015343851</v>
       </c>
       <c r="G24">
-        <v>193962.4460879035</v>
+        <v>568.9660509968801</v>
       </c>
       <c r="H24">
-        <v>273969.20807363</v>
+        <v>962.554449576048</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C25">
-        <v>4096230</v>
+        <v>3908726</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1203,19 +1203,19 @@
         </is>
       </c>
       <c r="F25">
-        <v>146281.8006885618</v>
+        <v>49264.4917994983</v>
       </c>
       <c r="G25">
-        <v>119851.2501782821</v>
+        <v>37672.2455607545</v>
       </c>
       <c r="H25">
-        <v>170297.5382820359</v>
+        <v>65858.1716086629</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1224,32 +1224,32 @@
         </is>
       </c>
       <c r="C26">
-        <v>4144144</v>
+        <v>3908726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>21208</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>15121.70409085993</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>27455.7644142777</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1258,32 +1258,32 @@
         </is>
       </c>
       <c r="C27">
-        <v>4144144</v>
+        <v>3908726</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F27">
-        <v>426.38685651087</v>
+        <v>46909.1718209481</v>
       </c>
       <c r="G27">
-        <v>352.253544849941</v>
+        <v>35071.5928746221</v>
       </c>
       <c r="H27">
-        <v>525.597869474415</v>
+        <v>60637.6507374221</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,32 +1292,32 @@
         </is>
       </c>
       <c r="C28">
-        <v>4144144</v>
+        <v>3908726</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F28">
-        <v>4766.185475625351</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>3908.59456313171</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>5986.59407013894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30-39</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1326,26 +1326,26 @@
         </is>
       </c>
       <c r="C29">
-        <v>4144144</v>
+        <v>3908726</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F29">
-        <v>35401.8139328565</v>
+        <v>79276.89547348869</v>
       </c>
       <c r="G29">
-        <v>24244.5385579803</v>
+        <v>63568.3063734423</v>
       </c>
       <c r="H29">
-        <v>50754.85073450441</v>
+        <v>94372.30382186361</v>
       </c>
     </row>
     <row r="30">
@@ -1356,15 +1356,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C30">
-        <v>4144144</v>
+        <v>4096230</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="F30">
-        <v>10901.72957676525</v>
+        <v>2780.422601653696</v>
       </c>
       <c r="G30">
-        <v>7356.45834177602</v>
+        <v>2330.600014968618</v>
       </c>
       <c r="H30">
-        <v>14831.47904260133</v>
+        <v>3260.06439065651</v>
       </c>
     </row>
     <row r="31">
@@ -1390,15 +1390,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C31">
-        <v>4144144</v>
+        <v>4096230</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>340.745943565134</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>274.2673331741521</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>420.161694727751</v>
       </c>
     </row>
     <row r="32">
@@ -1424,15 +1424,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C32">
-        <v>4144144</v>
+        <v>4096230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="F32">
-        <v>129451.1246432259</v>
+        <v>2289.499528412314</v>
       </c>
       <c r="G32">
-        <v>107006.4488749624</v>
+        <v>1827.303241610942</v>
       </c>
       <c r="H32">
-        <v>152123.3958443919</v>
+        <v>2851.59340962557</v>
       </c>
     </row>
     <row r="33">
@@ -1458,36 +1458,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C33">
-        <v>4144144</v>
+        <v>4096230</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>prevalence</t>
+          <t>incidence</t>
         </is>
       </c>
       <c r="F33">
-        <v>82777.48159718179</v>
+        <v>7789.04884493206</v>
       </c>
       <c r="G33">
-        <v>66083.9429747703</v>
+        <v>6537.24899800478</v>
       </c>
       <c r="H33">
-        <v>98645.3961044946</v>
+        <v>9261.19656670232</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1496,11 +1496,11 @@
         </is>
       </c>
       <c r="C34">
-        <v>4189428</v>
+        <v>4096230</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1509,19 +1509,19 @@
         </is>
       </c>
       <c r="F34">
-        <v>9268.175149006431</v>
+        <v>5843.84219410092</v>
       </c>
       <c r="G34">
-        <v>8009.4178693232</v>
+        <v>3783.80070456914</v>
       </c>
       <c r="H34">
-        <v>10483.10177700603</v>
+        <v>8315.68691031983</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1530,11 +1530,11 @@
         </is>
       </c>
       <c r="C35">
-        <v>4189428</v>
+        <v>4096230</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1543,19 +1543,19 @@
         </is>
       </c>
       <c r="F35">
-        <v>1184.421320507459</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>982.3889480264761</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>1413.964772140188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1564,11 +1564,11 @@
         </is>
       </c>
       <c r="C36">
-        <v>4189428</v>
+        <v>4096230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="F36">
-        <v>8323.432410617639</v>
+        <v>233272.265423371</v>
       </c>
       <c r="G36">
-        <v>6550.15596691663</v>
+        <v>193962.4460879035</v>
       </c>
       <c r="H36">
-        <v>10689.24244726687</v>
+        <v>273969.20807363</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1598,32 +1598,32 @@
         </is>
       </c>
       <c r="C37">
-        <v>4189428</v>
+        <v>4096230</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F37">
-        <v>173026.2383390926</v>
+        <v>24709.65879452023</v>
       </c>
       <c r="G37">
-        <v>112085.3092748197</v>
+        <v>20920</v>
       </c>
       <c r="H37">
-        <v>252325.24168495</v>
+        <v>28831.66500701612</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1632,32 +1632,32 @@
         </is>
       </c>
       <c r="C38">
-        <v>4189428</v>
+        <v>4096230</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F38">
-        <v>8491.401302624319</v>
+        <v>2614.481647266935</v>
       </c>
       <c r="G38">
-        <v>6008.042655458619</v>
+        <v>2093</v>
       </c>
       <c r="H38">
-        <v>11857.53248279074</v>
+        <v>3276.41579521866</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1666,32 +1666,32 @@
         </is>
       </c>
       <c r="C39">
-        <v>4189428</v>
+        <v>4096230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F39">
-        <v>780.37259398474</v>
+        <v>123159.6607962684</v>
       </c>
       <c r="G39">
-        <v>434.1799459347792</v>
+        <v>83353.8592906127</v>
       </c>
       <c r="H39">
-        <v>1178.025522044687</v>
+        <v>177200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1700,32 +1700,32 @@
         </is>
       </c>
       <c r="C40">
-        <v>4189428</v>
+        <v>4096230</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F40">
-        <v>241519.615139631</v>
+        <v>58060.15056777791</v>
       </c>
       <c r="G40">
-        <v>200137.2726359572</v>
+        <v>46225.6823146033</v>
       </c>
       <c r="H40">
-        <v>282858.023093132</v>
+        <v>70367</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1734,11 +1734,11 @@
         </is>
       </c>
       <c r="C41">
-        <v>4189428</v>
+        <v>4096230</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1747,37 +1747,37 @@
         </is>
       </c>
       <c r="F41">
-        <v>156242.6690374908</v>
+        <v>89759.8462277832</v>
       </c>
       <c r="G41">
-        <v>131891.3107798316</v>
+        <v>72539</v>
       </c>
       <c r="H41">
-        <v>183195.9932313872</v>
+        <v>109821</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C42">
-        <v>4123503</v>
+        <v>4096230</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F42">
@@ -1793,41 +1793,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C43">
-        <v>4123503</v>
+        <v>4096230</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F43">
-        <v>1240.23296731912</v>
+        <v>146281.8006885618</v>
       </c>
       <c r="G43">
-        <v>1050.270818401477</v>
+        <v>119851.2501782821</v>
       </c>
       <c r="H43">
-        <v>1471.406903694449</v>
+        <v>170297.5382820359</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1836,11 +1836,11 @@
         </is>
       </c>
       <c r="C44">
-        <v>4123503</v>
+        <v>4144144</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="F44">
-        <v>15234.66753207868</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>12795.31432586486</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>18343.15675212529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1870,11 +1870,11 @@
         </is>
       </c>
       <c r="C45">
-        <v>4123503</v>
+        <v>4144144</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1883,19 +1883,19 @@
         </is>
       </c>
       <c r="F45">
-        <v>61541.6836154451</v>
+        <v>426.38685651087</v>
       </c>
       <c r="G45">
-        <v>42881.1225305717</v>
+        <v>352.253544849941</v>
       </c>
       <c r="H45">
-        <v>84163.06044217839</v>
+        <v>525.597869474415</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1904,11 +1904,11 @@
         </is>
       </c>
       <c r="C46">
-        <v>4123503</v>
+        <v>4144144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1917,19 +1917,19 @@
         </is>
       </c>
       <c r="F46">
-        <v>16436.11038939894</v>
+        <v>4766.185475625351</v>
       </c>
       <c r="G46">
-        <v>12026.51454262601</v>
+        <v>3908.59456313171</v>
       </c>
       <c r="H46">
-        <v>21767.21167520286</v>
+        <v>5986.59407013894</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1938,11 +1938,11 @@
         </is>
       </c>
       <c r="C47">
-        <v>4123503</v>
+        <v>4144144</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="F47">
-        <v>692.354900230428</v>
+        <v>6383.83093763087</v>
       </c>
       <c r="G47">
-        <v>393.3236450672577</v>
+        <v>6383.83093763087</v>
       </c>
       <c r="H47">
-        <v>1034.814689669972</v>
+        <v>8113.966559473611</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1972,11 +1972,11 @@
         </is>
       </c>
       <c r="C48">
-        <v>4123503</v>
+        <v>4144144</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1985,19 +1985,19 @@
         </is>
       </c>
       <c r="F48">
-        <v>132657.768561709</v>
+        <v>10901.72957676525</v>
       </c>
       <c r="G48">
-        <v>109278.0916220621</v>
+        <v>7356.45834177602</v>
       </c>
       <c r="H48">
-        <v>155868.5791188676</v>
+        <v>14831.47904260133</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>40-49</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2006,45 +2006,45 @@
         </is>
       </c>
       <c r="C49">
-        <v>4123503</v>
+        <v>4144144</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>prevalence</t>
+          <t>incidence</t>
         </is>
       </c>
       <c r="F49">
-        <v>86520.97964761019</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>71537.8571400131</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>104645.1083910687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C50">
-        <v>4348515</v>
+        <v>4144144</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2053,232 +2053,232 @@
         </is>
       </c>
       <c r="F50">
-        <v>13144.66077896016</v>
+        <v>129451.1246432259</v>
       </c>
       <c r="G50">
-        <v>11411.01277183558</v>
+        <v>107006.4488749624</v>
       </c>
       <c r="H50">
-        <v>15322.59485314884</v>
+        <v>152123.3958443919</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C51">
-        <v>4348515</v>
+        <v>4144144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F51">
-        <v>2959.32167889886</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>2533.44626450858</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>3360.19042825555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C52">
-        <v>4348515</v>
+        <v>4144144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F52">
-        <v>20804.95890377918</v>
+        <v>3259.6969806059</v>
       </c>
       <c r="G52">
-        <v>16016.10807877293</v>
+        <v>2613.11606677353</v>
       </c>
       <c r="H52">
-        <v>27766.9372135923</v>
+        <v>4025.62434146514</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C53">
-        <v>4348515</v>
+        <v>4144144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F53">
-        <v>207015.537244565</v>
+        <v>136664.034848447</v>
       </c>
       <c r="G53">
-        <v>144441.2937341577</v>
+        <v>99574.02148120941</v>
       </c>
       <c r="H53">
-        <v>289649.735665997</v>
+        <v>190104.5504511171</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C54">
-        <v>4348515</v>
+        <v>4144144</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F54">
-        <v>16880.64121654448</v>
+        <v>44520</v>
       </c>
       <c r="G54">
-        <v>12486.55386155549</v>
+        <v>31889.7688759235</v>
       </c>
       <c r="H54">
-        <v>21546.83891656269</v>
+        <v>58637.80033125221</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C55">
-        <v>4348515</v>
+        <v>4144144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F55">
-        <v>1611.644963362494</v>
+        <v>137111.6315177955</v>
       </c>
       <c r="G55">
-        <v>909.85234953855</v>
+        <v>109343.53932446</v>
       </c>
       <c r="H55">
-        <v>2435.75615679975</v>
+        <v>167674.9989614138</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C56">
-        <v>4348515</v>
+        <v>4144144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F56">
-        <v>245938.52176707</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>209445.895514519</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>286563.948456743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C57">
-        <v>4348515</v>
+        <v>4144144</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2291,28 +2291,28 @@
         </is>
       </c>
       <c r="F57">
-        <v>165159.8670502452</v>
+        <v>82777.48159718179</v>
       </c>
       <c r="G57">
-        <v>141830.9300221652</v>
+        <v>66083.9429747703</v>
       </c>
       <c r="H57">
-        <v>195873.9200354734</v>
+        <v>98645.3961044946</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C58">
-        <v>4135955</v>
+        <v>4189428</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2325,28 +2325,28 @@
         </is>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>9268.175149006431</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>8009.4178693232</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>10483.10177700603</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C59">
-        <v>4135955</v>
+        <v>4189428</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2359,28 +2359,28 @@
         </is>
       </c>
       <c r="F59">
-        <v>3908.1674659415</v>
+        <v>1184.421320507459</v>
       </c>
       <c r="G59">
-        <v>3392.01124071847</v>
+        <v>982.3889480264761</v>
       </c>
       <c r="H59">
-        <v>4476.46523425307</v>
+        <v>1413.964772140188</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C60">
-        <v>4135955</v>
+        <v>4189428</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2393,28 +2393,28 @@
         </is>
       </c>
       <c r="F60">
-        <v>38407.7791813967</v>
+        <v>8323.432410617639</v>
       </c>
       <c r="G60">
-        <v>31800.2232209551</v>
+        <v>6550.15596691663</v>
       </c>
       <c r="H60">
-        <v>46280.0543478304</v>
+        <v>10689.24244726687</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C61">
-        <v>4135955</v>
+        <v>4189428</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2427,28 +2427,28 @@
         </is>
       </c>
       <c r="F61">
-        <v>109838.5222475847</v>
+        <v>20913.59180576165</v>
       </c>
       <c r="G61">
-        <v>83679.3277820583</v>
+        <v>18131.62374782994</v>
       </c>
       <c r="H61">
-        <v>141727.3307065134</v>
+        <v>23938.21520514674</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C62">
-        <v>4135955</v>
+        <v>4189428</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2461,28 +2461,28 @@
         </is>
       </c>
       <c r="F62">
-        <v>24441.548607311</v>
+        <v>8491.401302624319</v>
       </c>
       <c r="G62">
-        <v>18657.69892526098</v>
+        <v>6008.042655458619</v>
       </c>
       <c r="H62">
-        <v>30935.7108391935</v>
+        <v>11857.53248279074</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C63">
-        <v>4135955</v>
+        <v>4189428</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2495,28 +2495,28 @@
         </is>
       </c>
       <c r="F63">
-        <v>1408.285286009058</v>
+        <v>780.37259398474</v>
       </c>
       <c r="G63">
-        <v>763.292645741869</v>
+        <v>434.1799459347792</v>
       </c>
       <c r="H63">
-        <v>2132.837440622325</v>
+        <v>1178.025522044687</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C64">
-        <v>4135955</v>
+        <v>4189428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2529,32 +2529,32 @@
         </is>
       </c>
       <c r="F64">
-        <v>126822.2394861808</v>
+        <v>241519.615139631</v>
       </c>
       <c r="G64">
-        <v>107935.4326685209</v>
+        <v>200137.2726359572</v>
       </c>
       <c r="H64">
-        <v>148915.1175055146</v>
+        <v>282858.023093132</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>50-59</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C65">
-        <v>4135955</v>
+        <v>4189428</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="F65">
-        <v>84108.7901579273</v>
+        <v>85638.0315002884</v>
       </c>
       <c r="G65">
-        <v>70785.4793320352</v>
+        <v>75533</v>
       </c>
       <c r="H65">
-        <v>102599.4514352494</v>
+        <v>96171.01586957031</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2584,32 +2584,32 @@
         </is>
       </c>
       <c r="C66">
-        <v>4093762</v>
+        <v>4189428</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F66">
-        <v>15622.61700728103</v>
+        <v>8837.19360055847</v>
       </c>
       <c r="G66">
-        <v>13459.25387019072</v>
+        <v>7261</v>
       </c>
       <c r="H66">
-        <v>18102.28710574489</v>
+        <v>10601.12208131379</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2618,32 +2618,32 @@
         </is>
       </c>
       <c r="C67">
-        <v>4093762</v>
+        <v>4189428</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F67">
-        <v>5428.18953203978</v>
+        <v>350885.916170787</v>
       </c>
       <c r="G67">
-        <v>4666.76151903702</v>
+        <v>234498.3012163861</v>
       </c>
       <c r="H67">
-        <v>6129.160404917309</v>
+        <v>496001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2652,32 +2652,32 @@
         </is>
       </c>
       <c r="C68">
-        <v>4093762</v>
+        <v>4189428</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F68">
-        <v>53244.7833987288</v>
+        <v>156044.3889764351</v>
       </c>
       <c r="G68">
-        <v>41973.0675022009</v>
+        <v>128642.9159046172</v>
       </c>
       <c r="H68">
-        <v>68295.9997848974</v>
+        <v>180800</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2686,32 +2686,32 @@
         </is>
       </c>
       <c r="C69">
-        <v>4093762</v>
+        <v>4189428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F69">
-        <v>192498.4090463575</v>
+        <v>163141.6721896762</v>
       </c>
       <c r="G69">
-        <v>137010.6219645618</v>
+        <v>136339</v>
       </c>
       <c r="H69">
-        <v>265558.492611594</v>
+        <v>198250</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2720,32 +2720,32 @@
         </is>
       </c>
       <c r="C70">
-        <v>4093762</v>
+        <v>4189428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F70">
-        <v>20676.87550245501</v>
+        <v>2741.697263219582</v>
       </c>
       <c r="G70">
-        <v>16538.79093949113</v>
+        <v>1531.917228081883</v>
       </c>
       <c r="H70">
-        <v>24813.7423650053</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2754,45 +2754,45 @@
         </is>
       </c>
       <c r="C71">
-        <v>4093762</v>
+        <v>4189428</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F71">
-        <v>7677.992179072809</v>
+        <v>156242.6690374908</v>
       </c>
       <c r="G71">
-        <v>5489.16980499161</v>
+        <v>131891.3107798316</v>
       </c>
       <c r="H71">
-        <v>10336.80537125242</v>
+        <v>183195.9932313872</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C72">
-        <v>4093762</v>
+        <v>4123503</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2801,53 +2801,53 @@
         </is>
       </c>
       <c r="F72">
-        <v>234965.225608928</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>198240.7493503844</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>281018.986039141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C73">
-        <v>4093762</v>
+        <v>4123503</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>prevalence</t>
+          <t>incidence</t>
         </is>
       </c>
       <c r="F73">
-        <v>160247.3648157223</v>
+        <v>1240.23296731912</v>
       </c>
       <c r="G73">
-        <v>139865.1341066696</v>
+        <v>1050.270818401477</v>
       </c>
       <c r="H73">
-        <v>187631.6062714633</v>
+        <v>1471.406903694449</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2856,11 +2856,11 @@
         </is>
       </c>
       <c r="C74">
-        <v>3712396</v>
+        <v>4123503</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2869,19 +2869,19 @@
         </is>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>15234.66753207868</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>12795.31432586486</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>18343.15675212529</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2890,11 +2890,11 @@
         </is>
       </c>
       <c r="C75">
-        <v>3712396</v>
+        <v>4123503</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2903,19 +2903,19 @@
         </is>
       </c>
       <c r="F75">
-        <v>8565.906606127041</v>
+        <v>14267.06908943556</v>
       </c>
       <c r="G75">
-        <v>7550.00661288407</v>
+        <v>14267.06908943556</v>
       </c>
       <c r="H75">
-        <v>9693.834900589891</v>
+        <v>17399.690800297</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2924,11 +2924,11 @@
         </is>
       </c>
       <c r="C76">
-        <v>3712396</v>
+        <v>4123503</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2937,19 +2937,19 @@
         </is>
       </c>
       <c r="F76">
-        <v>83174.7541516168</v>
+        <v>16436.11038939894</v>
       </c>
       <c r="G76">
-        <v>70297.4639139136</v>
+        <v>12026.51454262601</v>
       </c>
       <c r="H76">
-        <v>99544.2631032246</v>
+        <v>21767.21167520286</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2958,11 +2958,11 @@
         </is>
       </c>
       <c r="C77">
-        <v>3712396</v>
+        <v>4123503</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2971,19 +2971,19 @@
         </is>
       </c>
       <c r="F77">
-        <v>163222.4780823567</v>
+        <v>692.354900230428</v>
       </c>
       <c r="G77">
-        <v>129679.5969152766</v>
+        <v>393.3236450672577</v>
       </c>
       <c r="H77">
-        <v>206133.7382829882</v>
+        <v>1034.814689669972</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2992,11 +2992,11 @@
         </is>
       </c>
       <c r="C78">
-        <v>3712396</v>
+        <v>4123503</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3005,19 +3005,19 @@
         </is>
       </c>
       <c r="F78">
-        <v>22165.25142549191</v>
+        <v>132657.768561709</v>
       </c>
       <c r="G78">
-        <v>16975.65208192233</v>
+        <v>109278.0916220621</v>
       </c>
       <c r="H78">
-        <v>28373.5550286708</v>
+        <v>155868.5791188676</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3026,32 +3026,32 @@
         </is>
       </c>
       <c r="C79">
-        <v>3712396</v>
+        <v>4123503</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F79">
-        <v>6703.400871315171</v>
+        <v>0</v>
       </c>
       <c r="G79">
-        <v>4777.49357909894</v>
+        <v>0</v>
       </c>
       <c r="H79">
-        <v>9202.63351794759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3060,32 +3060,32 @@
         </is>
       </c>
       <c r="C80">
-        <v>3712396</v>
+        <v>4123503</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F80">
-        <v>111857.4133838121</v>
+        <v>9166.224739733419</v>
       </c>
       <c r="G80">
-        <v>93601.7075846628</v>
+        <v>7570.49619348484</v>
       </c>
       <c r="H80">
-        <v>134612.3799020467</v>
+        <v>11050.4239161319</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>60-69</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3094,11 +3094,11 @@
         </is>
       </c>
       <c r="C81">
-        <v>3712396</v>
+        <v>4123503</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3107,155 +3107,155 @@
         </is>
       </c>
       <c r="F81">
-        <v>75017.0061361609</v>
+        <v>449299.70575818</v>
       </c>
       <c r="G81">
-        <v>64109.8420994783</v>
+        <v>335669.513349828</v>
       </c>
       <c r="H81">
-        <v>89284.61783718379</v>
+        <v>605091.142427915</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C82">
-        <v>2895313</v>
+        <v>4123503</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F82">
-        <v>12003.49943115682</v>
+        <v>83273</v>
       </c>
       <c r="G82">
-        <v>10057.83765630877</v>
+        <v>62013.5135583833</v>
       </c>
       <c r="H82">
-        <v>13997.50485873621</v>
+        <v>109450.0130890193</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C83">
-        <v>2895313</v>
+        <v>4123503</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F83">
-        <v>6628.26881662322</v>
+        <v>284387.965924969</v>
       </c>
       <c r="G83">
-        <v>5498.358158168499</v>
+        <v>237963.2159892332</v>
       </c>
       <c r="H83">
-        <v>7597.640997212209</v>
+        <v>330724.220672954</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C84">
-        <v>2895313</v>
+        <v>4123503</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F84">
-        <v>72806.0814283017</v>
+        <v>2428.643203235482</v>
       </c>
       <c r="G84">
-        <v>59630.4445086248</v>
+        <v>1367.439677331948</v>
       </c>
       <c r="H84">
-        <v>89920.5292159074</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C85">
-        <v>2895313</v>
+        <v>4123503</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F85">
-        <v>115733.2820015083</v>
+        <v>86520.97964761019</v>
       </c>
       <c r="G85">
-        <v>87164.4956575501</v>
+        <v>71537.8571400131</v>
       </c>
       <c r="H85">
-        <v>157621.5867337455</v>
+        <v>104645.1083910687</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3264,11 +3264,11 @@
         </is>
       </c>
       <c r="C86">
-        <v>2895313</v>
+        <v>4348515</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3277,19 +3277,19 @@
         </is>
       </c>
       <c r="F86">
-        <v>7687.25893147035</v>
+        <v>13144.66077896016</v>
       </c>
       <c r="G86">
-        <v>5145.03383591933</v>
+        <v>11411.01277183558</v>
       </c>
       <c r="H86">
-        <v>9803.38027173666</v>
+        <v>15322.59485314884</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3298,11 +3298,11 @@
         </is>
       </c>
       <c r="C87">
-        <v>2895313</v>
+        <v>4348515</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3311,19 +3311,19 @@
         </is>
       </c>
       <c r="F87">
-        <v>22542.40399869726</v>
+        <v>2959.32167889886</v>
       </c>
       <c r="G87">
-        <v>16874.51413104691</v>
+        <v>2533.44626450858</v>
       </c>
       <c r="H87">
-        <v>29295.2167889556</v>
+        <v>3360.19042825555</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3332,11 +3332,11 @@
         </is>
       </c>
       <c r="C88">
-        <v>2895313</v>
+        <v>4348515</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3345,19 +3345,19 @@
         </is>
       </c>
       <c r="F88">
-        <v>167808.5341038699</v>
+        <v>20804.95890377918</v>
       </c>
       <c r="G88">
-        <v>140071.6049851529</v>
+        <v>16016.10807877293</v>
       </c>
       <c r="H88">
-        <v>203208.4278806121</v>
+        <v>27766.9372135923</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3366,45 +3366,45 @@
         </is>
       </c>
       <c r="C89">
-        <v>2895313</v>
+        <v>4348515</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>prevalence</t>
+          <t>incidence</t>
         </is>
       </c>
       <c r="F89">
-        <v>116901.0548305752</v>
+        <v>36835.792824375</v>
       </c>
       <c r="G89">
-        <v>100298.281197842</v>
+        <v>32548.9001802982</v>
       </c>
       <c r="H89">
-        <v>138477.8619947699</v>
+        <v>41680.0145665961</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C90">
-        <v>2415116</v>
+        <v>4348515</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3413,32 +3413,32 @@
         </is>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>16880.64121654448</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>12486.55386155549</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>21546.83891656269</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C91">
-        <v>2415116</v>
+        <v>4348515</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3447,32 +3447,32 @@
         </is>
       </c>
       <c r="F91">
-        <v>9586.46164356291</v>
+        <v>1611.644963362494</v>
       </c>
       <c r="G91">
-        <v>8352.42772824541</v>
+        <v>909.85234953855</v>
       </c>
       <c r="H91">
-        <v>10786.74354258001</v>
+        <v>2435.75615679975</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C92">
-        <v>2415116</v>
+        <v>4348515</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3481,168 +3481,168 @@
         </is>
       </c>
       <c r="F92">
-        <v>85190.85256585319</v>
+        <v>245938.52176707</v>
       </c>
       <c r="G92">
-        <v>72453.9262130531</v>
+        <v>209445.895514519</v>
       </c>
       <c r="H92">
-        <v>101709.11322588</v>
+        <v>286563.948456743</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C93">
-        <v>2415116</v>
+        <v>4348515</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F93">
-        <v>129472.8523538039</v>
+        <v>136522.5734970159</v>
       </c>
       <c r="G93">
-        <v>106932.8251179074</v>
+        <v>121273</v>
       </c>
       <c r="H93">
-        <v>160617.2461313043</v>
+        <v>153992.991019909</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C94">
-        <v>2415116</v>
+        <v>4348515</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F94">
-        <v>6452.99163739923</v>
+        <v>21370.53436483235</v>
       </c>
       <c r="G94">
-        <v>4113.277834531113</v>
+        <v>17999</v>
       </c>
       <c r="H94">
-        <v>9602.92437355419</v>
+        <v>24400.5170658995</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C95">
-        <v>2415116</v>
+        <v>4348515</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F95">
-        <v>16421.21990261302</v>
+        <v>729119.4433403891</v>
       </c>
       <c r="G95">
-        <v>11814.10163785217</v>
+        <v>533772.390119602</v>
       </c>
       <c r="H95">
-        <v>21633.06626619551</v>
+        <v>985186</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C96">
-        <v>2415116</v>
+        <v>4348515</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F96">
-        <v>72489.4045295047</v>
+        <v>263743.802454246</v>
       </c>
       <c r="G96">
-        <v>59853.3813603249</v>
+        <v>226360.306708681</v>
       </c>
       <c r="H96">
-        <v>88050.5168406843</v>
+        <v>302520</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>70-79</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C97">
-        <v>2415116</v>
+        <v>4348515</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F97">
-        <v>49226.4546632978</v>
+        <v>273908.516888504</v>
       </c>
       <c r="G97">
-        <v>41091.0967137373</v>
+        <v>235794</v>
       </c>
       <c r="H97">
-        <v>59910.9218070762</v>
+        <v>317645</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3672,32 +3672,32 @@
         </is>
       </c>
       <c r="C98">
-        <v>1968073</v>
+        <v>4348515</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F98">
-        <v>8668.09191063441</v>
+        <v>13558.18340507614</v>
       </c>
       <c r="G98">
-        <v>6433.961569150029</v>
+        <v>9682.85184559496</v>
       </c>
       <c r="H98">
-        <v>10484.25158526308</v>
+        <v>17559</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3706,45 +3706,45 @@
         </is>
       </c>
       <c r="C99">
-        <v>1968073</v>
+        <v>4348515</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F99">
-        <v>7581.45858812107</v>
+        <v>165159.8670502452</v>
       </c>
       <c r="G99">
-        <v>5520.009710476619</v>
+        <v>141830.9300221652</v>
       </c>
       <c r="H99">
-        <v>9126.428487504822</v>
+        <v>195873.9200354734</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C100">
-        <v>1968073</v>
+        <v>4135955</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3753,32 +3753,32 @@
         </is>
       </c>
       <c r="F100">
-        <v>80236.9146850743</v>
+        <v>0</v>
       </c>
       <c r="G100">
-        <v>65394.6810714758</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>100209.7975860125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C101">
-        <v>1968073</v>
+        <v>4135955</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3787,32 +3787,32 @@
         </is>
       </c>
       <c r="F101">
-        <v>70158.3338033584</v>
+        <v>3908.1674659415</v>
       </c>
       <c r="G101">
-        <v>55062.7482505098</v>
+        <v>3392.01124071847</v>
       </c>
       <c r="H101">
-        <v>85671.54205139389</v>
+        <v>4476.46523425307</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C102">
-        <v>1968073</v>
+        <v>4135955</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3821,32 +3821,32 @@
         </is>
       </c>
       <c r="F102">
-        <v>547.47190579133</v>
+        <v>38407.7791813967</v>
       </c>
       <c r="G102">
-        <v>320.868424591632</v>
+        <v>31800.2232209551</v>
       </c>
       <c r="H102">
-        <v>842.835998368727</v>
+        <v>46280.0543478304</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C103">
-        <v>1968073</v>
+        <v>4135955</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3855,32 +3855,32 @@
         </is>
       </c>
       <c r="F103">
-        <v>44003.8173551204</v>
+        <v>39194.2450368637</v>
       </c>
       <c r="G103">
-        <v>34345.9005165165</v>
+        <v>39194.2450368637</v>
       </c>
       <c r="H103">
-        <v>55545.745073194</v>
+        <v>45329.4184830017</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C104">
-        <v>1968073</v>
+        <v>4135955</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3889,53 +3889,53 @@
         </is>
       </c>
       <c r="F104">
-        <v>117265.8573828332</v>
+        <v>24441.548607311</v>
       </c>
       <c r="G104">
-        <v>98856.42737522451</v>
+        <v>18657.69892526098</v>
       </c>
       <c r="H104">
-        <v>139076.7186953186</v>
+        <v>30935.7108391935</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C105">
-        <v>1968073</v>
+        <v>4135955</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>prevalence</t>
+          <t>incidence</t>
         </is>
       </c>
       <c r="F105">
-        <v>85037.95386846241</v>
+        <v>1408.285286009058</v>
       </c>
       <c r="G105">
-        <v>70932.42273714399</v>
+        <v>763.292645741869</v>
       </c>
       <c r="H105">
-        <v>102004.2243420075</v>
+        <v>2132.837440622325</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3944,11 +3944,11 @@
         </is>
       </c>
       <c r="C106">
-        <v>1175917</v>
+        <v>4135955</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3957,19 +3957,19 @@
         </is>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>126822.2394861808</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>107935.4326685209</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>148915.1175055146</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3978,32 +3978,32 @@
         </is>
       </c>
       <c r="C107">
-        <v>1175917</v>
+        <v>4135955</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F107">
-        <v>6941.62391878595</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>5729.82934626112</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>8071.50785063476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4012,32 +4012,32 @@
         </is>
       </c>
       <c r="C108">
-        <v>1175917</v>
+        <v>4135955</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F108">
-        <v>62079.7747924685</v>
+        <v>27339.7469066948</v>
       </c>
       <c r="G108">
-        <v>52181.3995846667</v>
+        <v>23281.85866455445</v>
       </c>
       <c r="H108">
-        <v>73753.4604143567</v>
+        <v>31660.2958807456</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4046,32 +4046,32 @@
         </is>
       </c>
       <c r="C109">
-        <v>1175917</v>
+        <v>4135955</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F109">
-        <v>66311.0848307889</v>
+        <v>974612.971159931</v>
       </c>
       <c r="G109">
-        <v>55688.6842924363</v>
+        <v>794701.4133052221</v>
       </c>
       <c r="H109">
-        <v>77159.4856814793</v>
+        <v>1197574.063864425</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4080,32 +4080,32 @@
         </is>
       </c>
       <c r="C110">
-        <v>1175917</v>
+        <v>4135955</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F110">
-        <v>261.1708863250419</v>
+        <v>212135</v>
       </c>
       <c r="G110">
-        <v>143.0429946666646</v>
+        <v>168909.7723314771</v>
       </c>
       <c r="H110">
-        <v>408.676120122366</v>
+        <v>264234.821222853</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4114,32 +4114,32 @@
         </is>
       </c>
       <c r="C111">
-        <v>1175917</v>
+        <v>4135955</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F111">
-        <v>23795.9977544299</v>
+        <v>461051.872558071</v>
       </c>
       <c r="G111">
-        <v>17938.90857726559</v>
+        <v>398291.834202194</v>
       </c>
       <c r="H111">
-        <v>31359.2314898685</v>
+        <v>521026.694413284</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>80-89</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4148,59 +4148,2915 @@
         </is>
       </c>
       <c r="C112">
-        <v>1175917</v>
+        <v>4135955</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>incidence</t>
+          <t>prevalence</t>
         </is>
       </c>
       <c r="F112">
-        <v>37137.7466580992</v>
+        <v>11325.36429697512</v>
       </c>
       <c r="G112">
-        <v>31019.4355344466</v>
+        <v>8180.37193892305</v>
       </c>
       <c r="H112">
-        <v>44507.5568664808</v>
+        <v>14941</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>4135955</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F113">
+        <v>84108.7901579273</v>
+      </c>
+      <c r="G113">
+        <v>70785.4793320352</v>
+      </c>
+      <c r="H113">
+        <v>102599.4514352494</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>4093762</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F114">
+        <v>15622.61700728103</v>
+      </c>
+      <c r="G114">
+        <v>13459.25387019072</v>
+      </c>
+      <c r="H114">
+        <v>18102.28710574489</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>4093762</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F115">
+        <v>5428.18953203978</v>
+      </c>
+      <c r="G115">
+        <v>4666.76151903702</v>
+      </c>
+      <c r="H115">
+        <v>6129.160404917309</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>4093762</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F116">
+        <v>53244.7833987288</v>
+      </c>
+      <c r="G116">
+        <v>41973.0675022009</v>
+      </c>
+      <c r="H116">
+        <v>68295.9997848974</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>4093762</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F117">
+        <v>52929.6364839817</v>
+      </c>
+      <c r="G117">
+        <v>46726.16441236431</v>
+      </c>
+      <c r="H117">
+        <v>60675.8942908562</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>4093762</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F118">
+        <v>20676.87550245501</v>
+      </c>
+      <c r="G118">
+        <v>16538.79093949113</v>
+      </c>
+      <c r="H118">
+        <v>24813.7423650053</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>4093762</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F119">
+        <v>7677.992179072809</v>
+      </c>
+      <c r="G119">
+        <v>5489.16980499161</v>
+      </c>
+      <c r="H119">
+        <v>10336.80537125242</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>4093762</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F120">
+        <v>234965.225608928</v>
+      </c>
+      <c r="G120">
+        <v>198240.7493503844</v>
+      </c>
+      <c r="H120">
+        <v>281018.986039141</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>4093762</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F121">
+        <v>184886.6280794348</v>
+      </c>
+      <c r="G121">
+        <v>166860</v>
+      </c>
+      <c r="H121">
+        <v>206940.1563436781</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>4093762</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F122">
+        <v>37774.57663259409</v>
+      </c>
+      <c r="G122">
+        <v>32597</v>
+      </c>
+      <c r="H122">
+        <v>42689.4072789789</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>4093762</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F123">
+        <v>1220763.435758051</v>
+      </c>
+      <c r="G123">
+        <v>1000598.670460329</v>
+      </c>
+      <c r="H123">
+        <v>1514691</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>4093762</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F124">
+        <v>361464.900502786</v>
+      </c>
+      <c r="G124">
+        <v>311853.333604746</v>
+      </c>
+      <c r="H124">
+        <v>415845</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>4093762</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F125">
+        <v>427452.090995163</v>
+      </c>
+      <c r="G125">
+        <v>375142</v>
+      </c>
+      <c r="H125">
+        <v>488704</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>4093762</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F126">
+        <v>39368.7068791198</v>
+      </c>
+      <c r="G126">
+        <v>30644.78795560553</v>
+      </c>
+      <c r="H126">
+        <v>49695</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>4093762</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F127">
+        <v>160247.3648157223</v>
+      </c>
+      <c r="G127">
+        <v>139865.1341066696</v>
+      </c>
+      <c r="H127">
+        <v>187631.6062714633</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>3712396</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>3712396</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F129">
+        <v>8565.906606127041</v>
+      </c>
+      <c r="G129">
+        <v>7550.00661288407</v>
+      </c>
+      <c r="H129">
+        <v>9693.834900589891</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>3712396</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F130">
+        <v>83174.7541516168</v>
+      </c>
+      <c r="G130">
+        <v>70297.4639139136</v>
+      </c>
+      <c r="H130">
+        <v>99544.2631032246</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>3712396</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F131">
+        <v>81239.3323963578</v>
+      </c>
+      <c r="G131">
+        <v>81239.3323963578</v>
+      </c>
+      <c r="H131">
+        <v>93708.51616471491</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>3712396</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F132">
+        <v>22165.25142549191</v>
+      </c>
+      <c r="G132">
+        <v>16975.65208192233</v>
+      </c>
+      <c r="H132">
+        <v>28373.5550286708</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>3712396</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F133">
+        <v>6703.400871315171</v>
+      </c>
+      <c r="G133">
+        <v>4777.49357909894</v>
+      </c>
+      <c r="H133">
+        <v>9202.63351794759</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>3712396</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F134">
+        <v>111857.4133838121</v>
+      </c>
+      <c r="G134">
+        <v>93601.7075846628</v>
+      </c>
+      <c r="H134">
+        <v>134612.3799020467</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>3712396</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>3712396</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F136">
+        <v>56501.6495148951</v>
+      </c>
+      <c r="G136">
+        <v>48684.6909614406</v>
+      </c>
+      <c r="H136">
+        <v>65214.9225511678</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>3712396</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F137">
+        <v>1673112.488097569</v>
+      </c>
+      <c r="G137">
+        <v>1434751.812868063</v>
+      </c>
+      <c r="H137">
+        <v>1939968.805670462</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>3712396</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F138">
+        <v>439007</v>
+      </c>
+      <c r="G138">
+        <v>352041.426963587</v>
+      </c>
+      <c r="H138">
+        <v>538422.819965712</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>3712396</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F139">
+        <v>609181.231447932</v>
+      </c>
+      <c r="G139">
+        <v>545910.333418654</v>
+      </c>
+      <c r="H139">
+        <v>668195.484342469</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>3712396</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F140">
+        <v>33507.1508463348</v>
+      </c>
+      <c r="G140">
+        <v>26162.53476050502</v>
+      </c>
+      <c r="H140">
+        <v>41898</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>60-69</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>3712396</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F141">
+        <v>75017.0061361609</v>
+      </c>
+      <c r="G141">
+        <v>64109.8420994783</v>
+      </c>
+      <c r="H141">
+        <v>89284.61783718379</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>2895313</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F142">
+        <v>12003.49943115682</v>
+      </c>
+      <c r="G142">
+        <v>10057.83765630877</v>
+      </c>
+      <c r="H142">
+        <v>13997.50485873621</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>2895313</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F143">
+        <v>6628.26881662322</v>
+      </c>
+      <c r="G143">
+        <v>5498.358158168499</v>
+      </c>
+      <c r="H143">
+        <v>7597.640997212209</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>2895313</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F144">
+        <v>72806.0814283017</v>
+      </c>
+      <c r="G144">
+        <v>59630.4445086248</v>
+      </c>
+      <c r="H144">
+        <v>89920.5292159074</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>2895313</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F145">
+        <v>50947.5999743147</v>
+      </c>
+      <c r="G145">
+        <v>43622.9090396478</v>
+      </c>
+      <c r="H145">
+        <v>58452.5861856425</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>2895313</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F146">
+        <v>7687.25893147035</v>
+      </c>
+      <c r="G146">
+        <v>5145.03383591933</v>
+      </c>
+      <c r="H146">
+        <v>9803.38027173666</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>2895313</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F147">
+        <v>22542.40399869726</v>
+      </c>
+      <c r="G147">
+        <v>16874.51413104691</v>
+      </c>
+      <c r="H147">
+        <v>29295.2167889556</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>2895313</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F148">
+        <v>167808.5341038699</v>
+      </c>
+      <c r="G148">
+        <v>140071.6049851529</v>
+      </c>
+      <c r="H148">
+        <v>203208.4278806121</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>2895313</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F149">
+        <v>149834.256723432</v>
+      </c>
+      <c r="G149">
+        <v>132745</v>
+      </c>
+      <c r="H149">
+        <v>166844.3504620524</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>2895313</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F150">
+        <v>43404.2656423537</v>
+      </c>
+      <c r="G150">
+        <v>35750</v>
+      </c>
+      <c r="H150">
+        <v>50093.3844411618</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>2895313</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F151">
+        <v>1391025.6218306</v>
+      </c>
+      <c r="G151">
+        <v>1201697.512051143</v>
+      </c>
+      <c r="H151">
+        <v>1610792</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>2895313</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F152">
+        <v>313253.1752735859</v>
+      </c>
+      <c r="G152">
+        <v>265266.342607405</v>
+      </c>
+      <c r="H152">
+        <v>365144</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>2895313</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F153">
+        <v>383172.734972509</v>
+      </c>
+      <c r="G153">
+        <v>345571</v>
+      </c>
+      <c r="H153">
+        <v>426656</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>2895313</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F154">
+        <v>118039.6406399182</v>
+      </c>
+      <c r="G154">
+        <v>95695.75696296859</v>
+      </c>
+      <c r="H154">
+        <v>143118</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>2895313</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F155">
+        <v>116901.0548305752</v>
+      </c>
+      <c r="G155">
+        <v>100298.281197842</v>
+      </c>
+      <c r="H155">
+        <v>138477.8619947699</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>2415116</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>2415116</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F157">
+        <v>9586.46164356291</v>
+      </c>
+      <c r="G157">
+        <v>8352.42772824541</v>
+      </c>
+      <c r="H157">
+        <v>10786.74354258001</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>2415116</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F158">
+        <v>85190.85256585319</v>
+      </c>
+      <c r="G158">
+        <v>72453.9262130531</v>
+      </c>
+      <c r="H158">
+        <v>101709.11322588</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>2415116</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F159">
+        <v>79995.6032457767</v>
+      </c>
+      <c r="G159">
+        <v>79995.6032457767</v>
+      </c>
+      <c r="H159">
+        <v>91482.6939187644</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>2415116</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F160">
+        <v>6452.99163739923</v>
+      </c>
+      <c r="G160">
+        <v>4113.277834531113</v>
+      </c>
+      <c r="H160">
+        <v>9602.92437355419</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>2415116</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F161">
+        <v>16421.21990261302</v>
+      </c>
+      <c r="G161">
+        <v>11814.10163785217</v>
+      </c>
+      <c r="H161">
+        <v>21633.06626619551</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>2415116</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F162">
+        <v>72489.4045295047</v>
+      </c>
+      <c r="G162">
+        <v>59853.3813603249</v>
+      </c>
+      <c r="H162">
+        <v>88050.5168406843</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>2415116</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>2415116</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F164">
+        <v>58679.5099121675</v>
+      </c>
+      <c r="G164">
+        <v>50055.8959580345</v>
+      </c>
+      <c r="H164">
+        <v>67812.38334202379</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>2415116</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F165">
+        <v>1592737.563103407</v>
+      </c>
+      <c r="G165">
+        <v>1444309.081912251</v>
+      </c>
+      <c r="H165">
+        <v>1756282.175781452</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>2415116</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F166">
+        <v>406114</v>
+      </c>
+      <c r="G166">
+        <v>328812.9207467959</v>
+      </c>
+      <c r="H166">
+        <v>488402.763682322</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>2415116</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F167">
+        <v>457428.827444336</v>
+      </c>
+      <c r="G167">
+        <v>413454.906954782</v>
+      </c>
+      <c r="H167">
+        <v>499768.781394868</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>2415116</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F168">
+        <v>88957.74294556101</v>
+      </c>
+      <c r="G168">
+        <v>70764.70950128129</v>
+      </c>
+      <c r="H168">
+        <v>108849</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>70-79</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>2415116</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F169">
+        <v>49226.4546632978</v>
+      </c>
+      <c r="G169">
+        <v>41091.0967137373</v>
+      </c>
+      <c r="H169">
+        <v>59910.9218070762</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
           <t>80-89</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C113">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>1968073</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F170">
+        <v>8668.09191063441</v>
+      </c>
+      <c r="G170">
+        <v>6433.961569150029</v>
+      </c>
+      <c r="H170">
+        <v>10484.25158526308</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>1968073</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F171">
+        <v>7581.45858812107</v>
+      </c>
+      <c r="G171">
+        <v>5520.009710476619</v>
+      </c>
+      <c r="H171">
+        <v>9126.428487504822</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>1968073</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F172">
+        <v>80236.9146850743</v>
+      </c>
+      <c r="G172">
+        <v>65394.6810714758</v>
+      </c>
+      <c r="H172">
+        <v>100209.7975860125</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>1968073</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F173">
+        <v>45367.1448465515</v>
+      </c>
+      <c r="G173">
+        <v>35577.31746432321</v>
+      </c>
+      <c r="H173">
+        <v>53575.4514266163</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>1968073</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F174">
+        <v>547.47190579133</v>
+      </c>
+      <c r="G174">
+        <v>320.868424591632</v>
+      </c>
+      <c r="H174">
+        <v>842.835998368727</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>1968073</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F175">
+        <v>44003.8173551204</v>
+      </c>
+      <c r="G175">
+        <v>34345.9005165165</v>
+      </c>
+      <c r="H175">
+        <v>55545.745073194</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>1968073</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F176">
+        <v>117265.8573828332</v>
+      </c>
+      <c r="G176">
+        <v>98856.42737522451</v>
+      </c>
+      <c r="H176">
+        <v>139076.7186953186</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>1968073</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F177">
+        <v>106601.7145072677</v>
+      </c>
+      <c r="G177">
+        <v>91338</v>
+      </c>
+      <c r="H177">
+        <v>120354.664525762</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>1968073</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F178">
+        <v>38742.6476557627</v>
+      </c>
+      <c r="G178">
+        <v>28766</v>
+      </c>
+      <c r="H178">
+        <v>47236.2135408294</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>1968073</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F179">
+        <v>1315388.483780277</v>
+      </c>
+      <c r="G179">
+        <v>1195345.047973889</v>
+      </c>
+      <c r="H179">
+        <v>1442027</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>1968073</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F180">
+        <v>217037.7811413726</v>
+      </c>
+      <c r="G180">
+        <v>171878.3272952943</v>
+      </c>
+      <c r="H180">
+        <v>262363</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>1968073</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F181">
+        <v>260195.950462987</v>
+      </c>
+      <c r="G181">
+        <v>233325</v>
+      </c>
+      <c r="H181">
+        <v>287604</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>1968073</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F182">
+        <v>249162.613320125</v>
+      </c>
+      <c r="G182">
+        <v>207390.1828363998</v>
+      </c>
+      <c r="H182">
+        <v>297015</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>1968073</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F183">
+        <v>85037.95386846241</v>
+      </c>
+      <c r="G183">
+        <v>70932.42273714399</v>
+      </c>
+      <c r="H183">
+        <v>102004.2243420075</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C184">
         <v>1175917</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>1175917</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F185">
+        <v>6941.62391878595</v>
+      </c>
+      <c r="G185">
+        <v>5729.82934626112</v>
+      </c>
+      <c r="H185">
+        <v>8071.50785063476</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>1175917</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F186">
+        <v>62079.7747924685</v>
+      </c>
+      <c r="G186">
+        <v>52181.3995846667</v>
+      </c>
+      <c r="H186">
+        <v>73753.4604143567</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>1175917</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F187">
+        <v>48590.5207135628</v>
+      </c>
+      <c r="G187">
+        <v>48590.5207135628</v>
+      </c>
+      <c r="H187">
+        <v>55590.7076884183</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>1175917</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F188">
+        <v>261.1708863250419</v>
+      </c>
+      <c r="G188">
+        <v>143.0429946666646</v>
+      </c>
+      <c r="H188">
+        <v>408.676120122366</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>1175917</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F189">
+        <v>23795.9977544299</v>
+      </c>
+      <c r="G189">
+        <v>17938.90857726559</v>
+      </c>
+      <c r="H189">
+        <v>31359.2314898685</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>1175917</v>
+      </c>
+      <c r="D190" t="inlineStr">
         <is>
           <t>dep</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>prevalence</t>
-        </is>
-      </c>
-      <c r="F113">
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>incidence</t>
+        </is>
+      </c>
+      <c r="F190">
+        <v>37137.7466580992</v>
+      </c>
+      <c r="G190">
+        <v>31019.4355344466</v>
+      </c>
+      <c r="H190">
+        <v>44507.5568664808</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>1175917</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F191">
+        <v>0</v>
+      </c>
+      <c r="G191">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>1175917</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F192">
+        <v>32555.8256277544</v>
+      </c>
+      <c r="G192">
+        <v>26911.2704874796</v>
+      </c>
+      <c r="H192">
+        <v>38444.153582105</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>1175917</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F193">
+        <v>977089.363249509</v>
+      </c>
+      <c r="G193">
+        <v>916453.9161541241</v>
+      </c>
+      <c r="H193">
+        <v>1041142.862792277</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>1175917</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F194">
+        <v>179569</v>
+      </c>
+      <c r="G194">
+        <v>144000.0786393438</v>
+      </c>
+      <c r="H194">
+        <v>222059.5935761069</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>1175917</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F195">
+        <v>222083.5687486358</v>
+      </c>
+      <c r="G195">
+        <v>198329.6247482295</v>
+      </c>
+      <c r="H195">
+        <v>245742.870866628</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>1175917</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F196">
+        <v>132901.6026984219</v>
+      </c>
+      <c r="G196">
+        <v>107027.7804760202</v>
+      </c>
+      <c r="H196">
+        <v>162854</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>80-89</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>1175917</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>prevalence</t>
+        </is>
+      </c>
+      <c r="F197">
         <v>25963.9986561012</v>
       </c>
-      <c r="G113">
+      <c r="G197">
         <v>21080.44185104526</v>
       </c>
-      <c r="H113">
+      <c r="H197">
         <v>31930.0031682083</v>
       </c>
     </row>
